--- a/data/Brienz (BE)/investment_decision/Brienz BE_district_investment_decision.xlsx
+++ b/data/Brienz (BE)/investment_decision/Brienz BE_district_investment_decision.xlsx
@@ -17,8 +17,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt numFmtId="164" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="165" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
+    <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -58,13 +58,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K36"/>
+  <dimension ref="A1:K16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -461,37 +460,37 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>scen_all_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>scen_all_candidate_unit</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_invested_available_unit</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>scen_cp_cu_candidate_unit</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>scen_cp_dr_invested_available_unit</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>scen_cp_dr_candidate_unit</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>scen_all_candidate_unit</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_invested_available_unit</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>scen_cp_cu_candidate_unit</t>
-        </is>
-      </c>
     </row>
     <row r="2">
-      <c r="A2" s="3" t="n">
+      <c r="A2" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B2" t="n">
@@ -512,7 +511,7 @@
         <v>0</v>
       </c>
       <c r="G2" t="n">
-        <v>21.84246242154624</v>
+        <v>5.869162553350398</v>
       </c>
       <c r="H2" t="n">
         <v>0</v>
@@ -524,11 +523,11 @@
         <v>0</v>
       </c>
       <c r="K2" t="n">
-        <v>5.869162553350398</v>
+        <v>21.84246242154624</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="3" t="n">
+      <c r="A3" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B3" t="n">
@@ -549,7 +548,7 @@
         <v>0</v>
       </c>
       <c r="G3" t="n">
-        <v>21.84246242154624</v>
+        <v>8.843686514793495</v>
       </c>
       <c r="H3" t="n">
         <v>0</v>
@@ -561,11 +560,11 @@
         <v>0</v>
       </c>
       <c r="K3" t="n">
-        <v>8.843686514793495</v>
+        <v>21.84246242154624</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="3" t="n">
+      <c r="A4" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B4" t="n">
@@ -586,7 +585,7 @@
         <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>21.84246242154624</v>
+        <v>10.60101926068374</v>
       </c>
       <c r="H4" t="n">
         <v>0</v>
@@ -598,11 +597,11 @@
         <v>0</v>
       </c>
       <c r="K4" t="n">
-        <v>10.60101926068374</v>
+        <v>21.84246242154624</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="3" t="n">
+      <c r="A5" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B5" t="n">
@@ -623,7 +622,7 @@
         <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>21.84246242154624</v>
+        <v>11.7486587012794</v>
       </c>
       <c r="H5" t="n">
         <v>0</v>
@@ -635,11 +634,11 @@
         <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>11.7486587012794</v>
+        <v>21.84246242154624</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="3" t="n">
+      <c r="A6" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B6" t="n">
@@ -660,7 +659,7 @@
         <v>0</v>
       </c>
       <c r="G6" t="n">
-        <v>21.84246242154624</v>
+        <v>12.55304003374661</v>
       </c>
       <c r="H6" t="n">
         <v>0</v>
@@ -672,15 +671,15 @@
         <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>12.55304003374661</v>
+        <v>21.84246242154624</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="3" t="n">
+      <c r="A7" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B7" t="n">
-        <v>0.5900172489155161</v>
+        <v>0.7067893416058824</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -694,30 +693,30 @@
         <v>21.84246242154624</v>
       </c>
       <c r="F7" t="n">
-        <v>0.5907079903559248</v>
+        <v>0.7067893416058824</v>
       </c>
       <c r="G7" t="n">
-        <v>21.84246242154624</v>
+        <v>5.869162553350398</v>
       </c>
       <c r="H7" t="n">
-        <v>0.5907079903559245</v>
+        <v>0.7067893416058824</v>
       </c>
       <c r="I7" t="n">
         <v>5.869162553350398</v>
       </c>
       <c r="J7" t="n">
-        <v>0.5900191681561998</v>
+        <v>0.7067893416058824</v>
       </c>
       <c r="K7" t="n">
-        <v>5.869162553350398</v>
+        <v>21.84246242154624</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="3" t="n">
+      <c r="A8" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B8" t="n">
-        <v>0.5970088641886732</v>
+        <v>0.8171980784588235</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -731,30 +730,30 @@
         <v>21.84246242154624</v>
       </c>
       <c r="F8" t="n">
-        <v>0.5974215186645091</v>
+        <v>0.840410766782353</v>
       </c>
       <c r="G8" t="n">
-        <v>21.84246242154624</v>
+        <v>8.843686514793495</v>
       </c>
       <c r="H8" t="n">
-        <v>0.5974248454516646</v>
+        <v>0.8276878736294118</v>
       </c>
       <c r="I8" t="n">
         <v>8.843686514793495</v>
       </c>
       <c r="J8" t="n">
-        <v>0.5974223154056243</v>
+        <v>0.8269956080199218</v>
       </c>
       <c r="K8" t="n">
-        <v>8.843686514793495</v>
+        <v>21.84246242154624</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="3" t="n">
+      <c r="A9" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B9" t="n">
-        <v>0.6025269980758214</v>
+        <v>0.9475689928381971</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -768,30 +767,30 @@
         <v>21.84246242154624</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6025269980758214</v>
+        <v>0.9452694466576642</v>
       </c>
       <c r="G9" t="n">
-        <v>21.84246242154624</v>
+        <v>10.60101926068374</v>
       </c>
       <c r="H9" t="n">
-        <v>0.6027276145098548</v>
+        <v>0.9448168721899781</v>
       </c>
       <c r="I9" t="n">
         <v>10.60101926068374</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6028149711492602</v>
+        <v>0.94978885900258</v>
       </c>
       <c r="K9" t="n">
-        <v>10.60101926068374</v>
+        <v>21.84246242154624</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="3" t="n">
+      <c r="A10" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B10" t="n">
-        <v>0.6091345203962116</v>
+        <v>1.019276111725179</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -805,30 +804,30 @@
         <v>21.84246242154624</v>
       </c>
       <c r="F10" t="n">
-        <v>0.6092342442145278</v>
+        <v>1.016690347625435</v>
       </c>
       <c r="G10" t="n">
-        <v>21.84246242154624</v>
+        <v>11.7486587012794</v>
       </c>
       <c r="H10" t="n">
-        <v>0.6092413821892025</v>
+        <v>1.009876605470913</v>
       </c>
       <c r="I10" t="n">
         <v>11.7486587012794</v>
       </c>
       <c r="J10" t="n">
-        <v>0.609235953707092</v>
+        <v>1.021470172270588</v>
       </c>
       <c r="K10" t="n">
-        <v>11.7486587012794</v>
+        <v>21.84246242154624</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="3" t="n">
+      <c r="A11" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B11" t="n">
-        <v>0.6029037312225273</v>
+        <v>1.016827659758692</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -842,26 +841,26 @@
         <v>21.84246242154624</v>
       </c>
       <c r="F11" t="n">
-        <v>0.6029502093809717</v>
+        <v>1.003294197832509</v>
       </c>
       <c r="G11" t="n">
-        <v>21.84246242154624</v>
+        <v>12.55304003374661</v>
       </c>
       <c r="H11" t="n">
-        <v>0.6030405205302972</v>
+        <v>1.003207072435619</v>
       </c>
       <c r="I11" t="n">
         <v>12.55304003374661</v>
       </c>
       <c r="J11" t="n">
-        <v>0.602955863721534</v>
+        <v>1.016855886937874</v>
       </c>
       <c r="K11" t="n">
-        <v>12.55304003374661</v>
+        <v>21.84246242154624</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="3" t="n">
+      <c r="A12" s="2" t="n">
         <v>46023</v>
       </c>
       <c r="B12" t="n">
@@ -898,7 +897,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="3" t="n">
+      <c r="A13" s="2" t="n">
         <v>47849</v>
       </c>
       <c r="B13" t="n">
@@ -935,7 +934,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="3" t="n">
+      <c r="A14" s="2" t="n">
         <v>49675</v>
       </c>
       <c r="B14" t="n">
@@ -972,7 +971,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="3" t="n">
+      <c r="A15" s="2" t="n">
         <v>51502</v>
       </c>
       <c r="B15" t="n">
@@ -1009,7 +1008,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="3" t="n">
+      <c r="A16" s="2" t="n">
         <v>53328</v>
       </c>
       <c r="B16" t="n">
@@ -1043,746 +1042,6 @@
       </c>
       <c r="K16" t="n">
         <v>1</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B17" t="n">
-        <v>0.0248042373014149</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Brienz BE</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>175</v>
-      </c>
-      <c r="E17" t="n">
-        <v>14.82885587689912</v>
-      </c>
-      <c r="F17" t="n">
-        <v>0.02483581405297673</v>
-      </c>
-      <c r="G17" t="n">
-        <v>14.82885587689912</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0.02483581405297672</v>
-      </c>
-      <c r="I17" t="n">
-        <v>14.82885587689912</v>
-      </c>
-      <c r="J17" t="n">
-        <v>0.02480432503813216</v>
-      </c>
-      <c r="K17" t="n">
-        <v>14.82885587689912</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B18" t="n">
-        <v>0.02512385399961665</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Brienz BE</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>175</v>
-      </c>
-      <c r="E18" t="n">
-        <v>14.82885587689912</v>
-      </c>
-      <c r="F18" t="n">
-        <v>0.0251427182042263</v>
-      </c>
-      <c r="G18" t="n">
-        <v>14.82885587689912</v>
-      </c>
-      <c r="H18" t="n">
-        <v>0.02514287028592484</v>
-      </c>
-      <c r="I18" t="n">
-        <v>14.82885587689912</v>
-      </c>
-      <c r="J18" t="n">
-        <v>0.02514275462667728</v>
-      </c>
-      <c r="K18" t="n">
-        <v>14.82885587689912</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B19" t="n">
-        <v>0.02537611154874344</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Brienz BE</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>175</v>
-      </c>
-      <c r="E19" t="n">
-        <v>14.82885587689912</v>
-      </c>
-      <c r="F19" t="n">
-        <v>0.02537611154874344</v>
-      </c>
-      <c r="G19" t="n">
-        <v>14.82885587689912</v>
-      </c>
-      <c r="H19" t="n">
-        <v>0.02538528258572782</v>
-      </c>
-      <c r="I19" t="n">
-        <v>14.82885587689912</v>
-      </c>
-      <c r="J19" t="n">
-        <v>0.02538927603210063</v>
-      </c>
-      <c r="K19" t="n">
-        <v>14.82885587689912</v>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B20" t="n">
-        <v>0.02771416611378664</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Brienz BE</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>175</v>
-      </c>
-      <c r="E20" t="n">
-        <v>14.82885587689912</v>
-      </c>
-      <c r="F20" t="n">
-        <v>0.02781320358252916</v>
-      </c>
-      <c r="G20" t="n">
-        <v>14.82885587689912</v>
-      </c>
-      <c r="H20" t="n">
-        <v>0.02824700730455029</v>
-      </c>
-      <c r="I20" t="n">
-        <v>14.82885587689912</v>
-      </c>
-      <c r="J20" t="n">
-        <v>0.02781490130950441</v>
-      </c>
-      <c r="K20" t="n">
-        <v>14.82885587689912</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B21" t="n">
-        <v>0.02799900219029792</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>DLVL_HotWaterTank_s_175 MWh_d_Brienz BE</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>175</v>
-      </c>
-      <c r="E21" t="n">
-        <v>14.82885587689912</v>
-      </c>
-      <c r="F21" t="n">
-        <v>0.02810047374634886</v>
-      </c>
-      <c r="G21" t="n">
-        <v>14.82885587689912</v>
-      </c>
-      <c r="H21" t="n">
-        <v>0.02872435677804121</v>
-      </c>
-      <c r="I21" t="n">
-        <v>14.82885587689912</v>
-      </c>
-      <c r="J21" t="n">
-        <v>0.0281128183562593</v>
-      </c>
-      <c r="K21" t="n">
-        <v>14.82885587689912</v>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B22" t="n">
-        <v>0</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Brienz BE</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>8</v>
-      </c>
-      <c r="E22" t="n">
-        <v>2.025714466045673</v>
-      </c>
-      <c r="F22" t="n">
-        <v>0</v>
-      </c>
-      <c r="G22" t="n">
-        <v>2.025714466045673</v>
-      </c>
-      <c r="H22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" t="n">
-        <v>0.02949217377677521</v>
-      </c>
-      <c r="J22" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" t="n">
-        <v>0.02949217377677521</v>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B23" t="n">
-        <v>0</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Brienz BE</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>8</v>
-      </c>
-      <c r="E23" t="n">
-        <v>2.025714466045673</v>
-      </c>
-      <c r="F23" t="n">
-        <v>0</v>
-      </c>
-      <c r="G23" t="n">
-        <v>2.025714466045673</v>
-      </c>
-      <c r="H23" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" t="n">
-        <v>0.05203676424019064</v>
-      </c>
-      <c r="J23" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" t="n">
-        <v>0.05203676424019064</v>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B24" t="n">
-        <v>0</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Brienz BE</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>8</v>
-      </c>
-      <c r="E24" t="n">
-        <v>2.025714466045673</v>
-      </c>
-      <c r="F24" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" t="n">
-        <v>2.025714466045673</v>
-      </c>
-      <c r="H24" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" t="n">
-        <v>0.07068565263757846</v>
-      </c>
-      <c r="J24" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" t="n">
-        <v>0.07068565263757846</v>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B25" t="n">
-        <v>0</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Brienz BE</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>8</v>
-      </c>
-      <c r="E25" t="n">
-        <v>2.025714466045673</v>
-      </c>
-      <c r="F25" t="n">
-        <v>0</v>
-      </c>
-      <c r="G25" t="n">
-        <v>2.025714466045673</v>
-      </c>
-      <c r="H25" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" t="n">
-        <v>0.08672893345412142</v>
-      </c>
-      <c r="J25" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" t="n">
-        <v>0.08672893345412142</v>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B26" t="n">
-        <v>0</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>DLVL_Li-ion_s_8 MWh_d_Brienz BE</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>8</v>
-      </c>
-      <c r="E26" t="n">
-        <v>2.025714466045673</v>
-      </c>
-      <c r="F26" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" t="n">
-        <v>2.025714466045673</v>
-      </c>
-      <c r="H26" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" t="n">
-        <v>0.1008722214311813</v>
-      </c>
-      <c r="J26" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" t="n">
-        <v>0.1008722214311813</v>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B27" t="n">
-        <v>0</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Brienz BE</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E27" t="n">
-        <v>3.904991741774792</v>
-      </c>
-      <c r="F27" t="n">
-        <v>0</v>
-      </c>
-      <c r="G27" t="n">
-        <v>3.904991741774792</v>
-      </c>
-      <c r="H27" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" t="n">
-        <v>0.056852383184145</v>
-      </c>
-      <c r="J27" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" t="n">
-        <v>0.056852383184145</v>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B28" t="n">
-        <v>0</v>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Brienz BE</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E28" t="n">
-        <v>3.904991741774792</v>
-      </c>
-      <c r="F28" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" t="n">
-        <v>3.904991741774792</v>
-      </c>
-      <c r="H28" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" t="n">
-        <v>0.1003118346798856</v>
-      </c>
-      <c r="J28" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" t="n">
-        <v>0.1003118346798856</v>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B29" t="n">
-        <v>0</v>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Brienz BE</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E29" t="n">
-        <v>3.904991741774792</v>
-      </c>
-      <c r="F29" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" t="n">
-        <v>3.904991741774792</v>
-      </c>
-      <c r="H29" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" t="n">
-        <v>0.1362614990603922</v>
-      </c>
-      <c r="J29" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" t="n">
-        <v>0.1362614990603922</v>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B30" t="n">
-        <v>0</v>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Brienz BE</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E30" t="n">
-        <v>3.904991741774792</v>
-      </c>
-      <c r="F30" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" t="n">
-        <v>3.904991741774792</v>
-      </c>
-      <c r="H30" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" t="n">
-        <v>0.1671883054537281</v>
-      </c>
-      <c r="J30" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" t="n">
-        <v>0.1671883054537281</v>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B31" t="n">
-        <v>0</v>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>DLVL_NMC_s_4.15 MWh_d_Brienz BE</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>4.15</v>
-      </c>
-      <c r="E31" t="n">
-        <v>3.904991741774792</v>
-      </c>
-      <c r="F31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G31" t="n">
-        <v>3.904991741774792</v>
-      </c>
-      <c r="H31" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" t="n">
-        <v>0.1944524750480603</v>
-      </c>
-      <c r="J31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" t="n">
-        <v>0.1944524750480603</v>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="3" t="n">
-        <v>46023</v>
-      </c>
-      <c r="B32" t="n">
-        <v>0</v>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Brienz BE</t>
-        </is>
-      </c>
-      <c r="D32" t="n">
-        <v>300</v>
-      </c>
-      <c r="E32" t="n">
-        <v>0.05401905242788461</v>
-      </c>
-      <c r="F32" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" t="n">
-        <v>0.05401905242788461</v>
-      </c>
-      <c r="H32" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" t="n">
-        <v>0.0007864579673806724</v>
-      </c>
-      <c r="J32" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" t="n">
-        <v>0.0007864579673806724</v>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="3" t="n">
-        <v>47849</v>
-      </c>
-      <c r="B33" t="n">
-        <v>0</v>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Brienz BE</t>
-        </is>
-      </c>
-      <c r="D33" t="n">
-        <v>300</v>
-      </c>
-      <c r="E33" t="n">
-        <v>0.05401905242788461</v>
-      </c>
-      <c r="F33" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" t="n">
-        <v>0.05401905242788461</v>
-      </c>
-      <c r="H33" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" t="n">
-        <v>0.001387647046405084</v>
-      </c>
-      <c r="J33" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" t="n">
-        <v>0.001387647046405084</v>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="3" t="n">
-        <v>49675</v>
-      </c>
-      <c r="B34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Brienz BE</t>
-        </is>
-      </c>
-      <c r="D34" t="n">
-        <v>300</v>
-      </c>
-      <c r="E34" t="n">
-        <v>0.05401905242788461</v>
-      </c>
-      <c r="F34" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" t="n">
-        <v>0.05401905242788461</v>
-      </c>
-      <c r="H34" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" t="n">
-        <v>0.001884950737002092</v>
-      </c>
-      <c r="J34" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" t="n">
-        <v>0.001884950737002092</v>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="3" t="n">
-        <v>51502</v>
-      </c>
-      <c r="B35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Brienz BE</t>
-        </is>
-      </c>
-      <c r="D35" t="n">
-        <v>300</v>
-      </c>
-      <c r="E35" t="n">
-        <v>0.05401905242788461</v>
-      </c>
-      <c r="F35" t="n">
-        <v>0</v>
-      </c>
-      <c r="G35" t="n">
-        <v>0.05401905242788461</v>
-      </c>
-      <c r="H35" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" t="n">
-        <v>0.002312771558776571</v>
-      </c>
-      <c r="J35" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" t="n">
-        <v>0.002312771558776571</v>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="3" t="n">
-        <v>53328</v>
-      </c>
-      <c r="B36" t="n">
-        <v>0</v>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>DLVL_NaS_s_300 MWh_d_Brienz BE</t>
-        </is>
-      </c>
-      <c r="D36" t="n">
-        <v>300</v>
-      </c>
-      <c r="E36" t="n">
-        <v>0.05401905242788461</v>
-      </c>
-      <c r="F36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" t="n">
-        <v>0.05401905242788461</v>
-      </c>
-      <c r="H36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" t="n">
-        <v>0.002689925904831501</v>
-      </c>
-      <c r="J36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" t="n">
-        <v>0.002689925904831501</v>
       </c>
     </row>
   </sheetData>
